--- a/lai/valuationquan/AIindex/AIinduindexmodel2.xlsx
+++ b/lai/valuationquan/AIindex/AIinduindexmodel2.xlsx
@@ -758,7 +758,7 @@
               <c:f>'model2(1)mean'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="111"/>
+                <c:ptCount val="112"/>
                 <c:pt idx="0">
                   <c:v>42825</c:v>
                 </c:pt>
@@ -1091,6 +1091,9 @@
                 </c:pt>
                 <c:pt idx="110">
                   <c:v>46171</c:v>
+                </c:pt>
+                <c:pt idx="111">
+                  <c:v>46203</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1100,7 +1103,7 @@
               <c:f>'model2(1)mean'!资金</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="111"/>
+                <c:ptCount val="112"/>
                 <c:pt idx="0">
                   <c:v>27.550142857142728</c:v>
                 </c:pt>
@@ -1432,6 +1435,9 @@
                   <c:v>4228.3228496289457</c:v>
                 </c:pt>
                 <c:pt idx="110">
+                  <c:v>4228.3228496289457</c:v>
+                </c:pt>
+                <c:pt idx="111">
                   <c:v>4228.3228496289457</c:v>
                 </c:pt>
               </c:numCache>
@@ -1475,7 +1481,7 @@
               <c:f>'model2(1)mean'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="111"/>
+                <c:ptCount val="112"/>
                 <c:pt idx="0">
                   <c:v>42825</c:v>
                 </c:pt>
@@ -1808,6 +1814,9 @@
                 </c:pt>
                 <c:pt idx="110">
                   <c:v>46171</c:v>
+                </c:pt>
+                <c:pt idx="111">
+                  <c:v>46203</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1817,7 +1826,7 @@
               <c:f>'model2(1)mean'!资产</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="111"/>
+                <c:ptCount val="112"/>
                 <c:pt idx="1">
                   <c:v>27.550142857142728</c:v>
                 </c:pt>
@@ -2146,6 +2155,9 @@
                   <c:v>5934.4066689137917</c:v>
                 </c:pt>
                 <c:pt idx="110">
+                  <c:v>5934.4066689137917</c:v>
+                </c:pt>
+                <c:pt idx="111">
                   <c:v>5934.4066689137917</c:v>
                 </c:pt>
               </c:numCache>
@@ -2189,7 +2201,7 @@
               <c:f>'model2(1)mean'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="111"/>
+                <c:ptCount val="112"/>
                 <c:pt idx="0">
                   <c:v>42825</c:v>
                 </c:pt>
@@ -2522,6 +2534,9 @@
                 </c:pt>
                 <c:pt idx="110">
                   <c:v>46171</c:v>
+                </c:pt>
+                <c:pt idx="111">
+                  <c:v>46203</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -2531,7 +2546,7 @@
               <c:f>'model2(1)mean'!金额</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="111"/>
+                <c:ptCount val="112"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -2863,6 +2878,9 @@
                   <c:v>1706.083819284846</c:v>
                 </c:pt>
                 <c:pt idx="110">
+                  <c:v>1706.083819284846</c:v>
+                </c:pt>
+                <c:pt idx="111">
                   <c:v>1706.083819284846</c:v>
                 </c:pt>
               </c:numCache>
@@ -2885,11 +2903,11 @@
         </c:dLbls>
         <c:marker val="1"/>
         <c:smooth val="0"/>
-        <c:axId val="99719808"/>
-        <c:axId val="103723776"/>
+        <c:axId val="479516160"/>
+        <c:axId val="479517696"/>
       </c:lineChart>
       <c:dateAx>
-        <c:axId val="99719808"/>
+        <c:axId val="479516160"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -2932,14 +2950,14 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="103723776"/>
+        <c:crossAx val="479517696"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblOffset val="100"/>
         <c:baseTimeUnit val="days"/>
       </c:dateAx>
       <c:valAx>
-        <c:axId val="103723776"/>
+        <c:axId val="479517696"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -2988,7 +3006,7 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="99719808"/>
+        <c:crossAx val="479516160"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -3185,7 +3203,7 @@
               <c:f>'model2(1)MA250'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="99"/>
+                <c:ptCount val="100"/>
                 <c:pt idx="0">
                   <c:v>43189</c:v>
                 </c:pt>
@@ -3482,6 +3500,9 @@
                 </c:pt>
                 <c:pt idx="98">
                   <c:v>46171</c:v>
+                </c:pt>
+                <c:pt idx="99">
+                  <c:v>46203</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -3491,7 +3512,7 @@
               <c:f>'model2(1)MA250'!资金</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="99"/>
+                <c:ptCount val="100"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -3788,6 +3809,9 @@
                 </c:pt>
                 <c:pt idx="98">
                   <c:v>6917.0073080000038</c:v>
+                </c:pt>
+                <c:pt idx="99">
+                  <c:v>7143.8348660000038</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -3830,7 +3854,7 @@
               <c:f>'model2(1)MA250'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="99"/>
+                <c:ptCount val="100"/>
                 <c:pt idx="0">
                   <c:v>43189</c:v>
                 </c:pt>
@@ -4127,6 +4151,9 @@
                 </c:pt>
                 <c:pt idx="98">
                   <c:v>46171</c:v>
+                </c:pt>
+                <c:pt idx="99">
+                  <c:v>46203</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -4136,7 +4163,7 @@
               <c:f>'model2(1)MA250'!资产</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="99"/>
+                <c:ptCount val="100"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -4433,6 +4460,9 @@
                 </c:pt>
                 <c:pt idx="98">
                   <c:v>9673.0994388317722</c:v>
+                </c:pt>
+                <c:pt idx="99">
+                  <c:v>9898.842556077434</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -4475,7 +4505,7 @@
               <c:f>'model2(1)MA250'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="99"/>
+                <c:ptCount val="100"/>
                 <c:pt idx="0">
                   <c:v>43189</c:v>
                 </c:pt>
@@ -4772,6 +4802,9 @@
                 </c:pt>
                 <c:pt idx="98">
                   <c:v>46171</c:v>
+                </c:pt>
+                <c:pt idx="99">
+                  <c:v>46203</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -4781,7 +4814,7 @@
               <c:f>'model2(1)MA250'!金额</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="99"/>
+                <c:ptCount val="100"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -5078,6 +5111,9 @@
                 </c:pt>
                 <c:pt idx="98">
                   <c:v>2756.0921308317684</c:v>
+                </c:pt>
+                <c:pt idx="99">
+                  <c:v>2755.0076900774302</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -5099,11 +5135,11 @@
         </c:dLbls>
         <c:marker val="1"/>
         <c:smooth val="0"/>
-        <c:axId val="399840000"/>
-        <c:axId val="399841536"/>
+        <c:axId val="479672960"/>
+        <c:axId val="479678848"/>
       </c:lineChart>
       <c:dateAx>
-        <c:axId val="399840000"/>
+        <c:axId val="479672960"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -5146,14 +5182,14 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="399841536"/>
+        <c:crossAx val="479678848"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblOffset val="100"/>
         <c:baseTimeUnit val="days"/>
       </c:dateAx>
       <c:valAx>
-        <c:axId val="399841536"/>
+        <c:axId val="479678848"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -5202,7 +5238,7 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="399840000"/>
+        <c:crossAx val="479672960"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -5310,7 +5346,7 @@
         <xdr:cNvPr id="2" name="图表 1">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{00000000-0008-0000-0000-000002000000}"/>
+              <a16:creationId xmlns="" xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000002000000}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -5353,7 +5389,7 @@
         <xdr:cNvPr id="2" name="图表 1">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{00000000-0008-0000-0100-000002000000}"/>
+              <a16:creationId xmlns="" xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0100-000002000000}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -5666,7 +5702,7 @@
   <sheetPr codeName="Sheet1">
     <tabColor rgb="FF00B050"/>
   </sheetPr>
-  <dimension ref="A1:AF114"/>
+  <dimension ref="A1:AF115"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="12"/>
   <cols>
     <col min="1" max="1" width="10" style="1" customWidth="1"/>
@@ -10350,6 +10386,41 @@
         <v>5934.4066689137917</v>
       </c>
     </row>
+    <row r="115" spans="1:11" ht="12.75">
+      <c r="A115" s="15">
+        <v>46203</v>
+      </c>
+      <c r="B115" s="25">
+        <v>1.7231300000000001</v>
+      </c>
+      <c r="C115" s="20">
+        <v>1.1747980992467859</v>
+      </c>
+      <c r="D115" s="21">
+        <v>0</v>
+      </c>
+      <c r="E115" s="22">
+        <v>0</v>
+      </c>
+      <c r="F115" s="22">
+        <v>0</v>
+      </c>
+      <c r="G115" s="22">
+        <v>0</v>
+      </c>
+      <c r="H115" s="22">
+        <v>4228.3228496289457</v>
+      </c>
+      <c r="I115" s="22">
+        <v>5934.4066689137917</v>
+      </c>
+      <c r="J115" s="22">
+        <v>1706.083819284846</v>
+      </c>
+      <c r="K115" s="21">
+        <v>5934.4066689137917</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
   <conditionalFormatting sqref="G3">
@@ -10366,7 +10437,7 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A1:AF102"/>
+  <dimension ref="A1:AF103"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="12"/>
   <cols>
     <col min="1" max="1" width="10" style="1" customWidth="1"/>
@@ -14508,6 +14579,41 @@
         <v>9655.027430831773</v>
       </c>
     </row>
+    <row r="103" spans="1:11" ht="12.75">
+      <c r="A103" s="15">
+        <v>46203</v>
+      </c>
+      <c r="B103" s="25">
+        <v>1.7231300000000001</v>
+      </c>
+      <c r="C103" s="20">
+        <v>1.8694703600000002</v>
+      </c>
+      <c r="D103" s="21">
+        <v>226.82755800000027</v>
+      </c>
+      <c r="E103" s="22">
+        <v>131.63693859430239</v>
+      </c>
+      <c r="F103" s="22">
+        <v>141.49549090646764</v>
+      </c>
+      <c r="G103" s="22">
+        <v>243.81512524566159</v>
+      </c>
+      <c r="H103" s="22">
+        <v>7143.8348660000038</v>
+      </c>
+      <c r="I103" s="22">
+        <v>9898.842556077434</v>
+      </c>
+      <c r="J103" s="22">
+        <v>2755.0076900774302</v>
+      </c>
+      <c r="K103" s="21">
+        <v>9655.027430831773</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
   <conditionalFormatting sqref="G3">

--- a/lai/valuationquan/AIindex/AIinduindexmodel2.xlsx
+++ b/lai/valuationquan/AIindex/AIinduindexmodel2.xlsx
@@ -758,7 +758,7 @@
               <c:f>'model2(1)mean'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="112"/>
+                <c:ptCount val="113"/>
                 <c:pt idx="0">
                   <c:v>42825</c:v>
                 </c:pt>
@@ -1094,6 +1094,9 @@
                 </c:pt>
                 <c:pt idx="111">
                   <c:v>46203</c:v>
+                </c:pt>
+                <c:pt idx="112">
+                  <c:v>46234</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1103,7 +1106,7 @@
               <c:f>'model2(1)mean'!资金</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="112"/>
+                <c:ptCount val="113"/>
                 <c:pt idx="0">
                   <c:v>27.550142857142728</c:v>
                 </c:pt>
@@ -1438,6 +1441,9 @@
                   <c:v>4228.3228496289457</c:v>
                 </c:pt>
                 <c:pt idx="111">
+                  <c:v>4228.3228496289457</c:v>
+                </c:pt>
+                <c:pt idx="112">
                   <c:v>4228.3228496289457</c:v>
                 </c:pt>
               </c:numCache>
@@ -1481,7 +1487,7 @@
               <c:f>'model2(1)mean'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="112"/>
+                <c:ptCount val="113"/>
                 <c:pt idx="0">
                   <c:v>42825</c:v>
                 </c:pt>
@@ -1817,6 +1823,9 @@
                 </c:pt>
                 <c:pt idx="111">
                   <c:v>46203</c:v>
+                </c:pt>
+                <c:pt idx="112">
+                  <c:v>46234</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1826,7 +1835,7 @@
               <c:f>'model2(1)mean'!资产</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="112"/>
+                <c:ptCount val="113"/>
                 <c:pt idx="1">
                   <c:v>27.550142857142728</c:v>
                 </c:pt>
@@ -2158,6 +2167,9 @@
                   <c:v>5934.4066689137917</c:v>
                 </c:pt>
                 <c:pt idx="111">
+                  <c:v>5934.4066689137917</c:v>
+                </c:pt>
+                <c:pt idx="112">
                   <c:v>5934.4066689137917</c:v>
                 </c:pt>
               </c:numCache>
@@ -2201,7 +2213,7 @@
               <c:f>'model2(1)mean'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="112"/>
+                <c:ptCount val="113"/>
                 <c:pt idx="0">
                   <c:v>42825</c:v>
                 </c:pt>
@@ -2537,6 +2549,9 @@
                 </c:pt>
                 <c:pt idx="111">
                   <c:v>46203</c:v>
+                </c:pt>
+                <c:pt idx="112">
+                  <c:v>46234</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -2546,7 +2561,7 @@
               <c:f>'model2(1)mean'!金额</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="112"/>
+                <c:ptCount val="113"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -2881,6 +2896,9 @@
                   <c:v>1706.083819284846</c:v>
                 </c:pt>
                 <c:pt idx="111">
+                  <c:v>1706.083819284846</c:v>
+                </c:pt>
+                <c:pt idx="112">
                   <c:v>1706.083819284846</c:v>
                 </c:pt>
               </c:numCache>
@@ -2903,11 +2921,11 @@
         </c:dLbls>
         <c:marker val="1"/>
         <c:smooth val="0"/>
-        <c:axId val="479516160"/>
-        <c:axId val="479517696"/>
+        <c:axId val="508912000"/>
+        <c:axId val="508914304"/>
       </c:lineChart>
       <c:dateAx>
-        <c:axId val="479516160"/>
+        <c:axId val="508912000"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -2950,14 +2968,14 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="479517696"/>
+        <c:crossAx val="508914304"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblOffset val="100"/>
         <c:baseTimeUnit val="days"/>
       </c:dateAx>
       <c:valAx>
-        <c:axId val="479517696"/>
+        <c:axId val="508914304"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -3006,7 +3024,7 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="479516160"/>
+        <c:crossAx val="508912000"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -3203,7 +3221,7 @@
               <c:f>'model2(1)MA250'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="100"/>
+                <c:ptCount val="101"/>
                 <c:pt idx="0">
                   <c:v>43189</c:v>
                 </c:pt>
@@ -3503,6 +3521,9 @@
                 </c:pt>
                 <c:pt idx="99">
                   <c:v>46203</c:v>
+                </c:pt>
+                <c:pt idx="100">
+                  <c:v>46234</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -3512,7 +3533,7 @@
               <c:f>'model2(1)MA250'!资金</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="100"/>
+                <c:ptCount val="101"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -3812,6 +3833,9 @@
                 </c:pt>
                 <c:pt idx="99">
                   <c:v>7143.8348660000038</c:v>
+                </c:pt>
+                <c:pt idx="100">
+                  <c:v>7502.8270800000037</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -3854,7 +3878,7 @@
               <c:f>'model2(1)MA250'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="100"/>
+                <c:ptCount val="101"/>
                 <c:pt idx="0">
                   <c:v>43189</c:v>
                 </c:pt>
@@ -4154,6 +4178,9 @@
                 </c:pt>
                 <c:pt idx="99">
                   <c:v>46203</c:v>
+                </c:pt>
+                <c:pt idx="100">
+                  <c:v>46234</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -4163,7 +4190,7 @@
               <c:f>'model2(1)MA250'!资产</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="100"/>
+                <c:ptCount val="101"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -4463,6 +4490,9 @@
                 </c:pt>
                 <c:pt idx="99">
                   <c:v>9898.842556077434</c:v>
+                </c:pt>
+                <c:pt idx="100">
+                  <c:v>10245.792088846385</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -4505,7 +4535,7 @@
               <c:f>'model2(1)MA250'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="100"/>
+                <c:ptCount val="101"/>
                 <c:pt idx="0">
                   <c:v>43189</c:v>
                 </c:pt>
@@ -4805,6 +4835,9 @@
                 </c:pt>
                 <c:pt idx="99">
                   <c:v>46203</c:v>
+                </c:pt>
+                <c:pt idx="100">
+                  <c:v>46234</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -4814,7 +4847,7 @@
               <c:f>'model2(1)MA250'!金额</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="100"/>
+                <c:ptCount val="101"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -5114,6 +5147,9 @@
                 </c:pt>
                 <c:pt idx="99">
                   <c:v>2755.0076900774302</c:v>
+                </c:pt>
+                <c:pt idx="100">
+                  <c:v>2742.9650088463814</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -5135,11 +5171,11 @@
         </c:dLbls>
         <c:marker val="1"/>
         <c:smooth val="0"/>
-        <c:axId val="479672960"/>
-        <c:axId val="479678848"/>
+        <c:axId val="676455936"/>
+        <c:axId val="676457472"/>
       </c:lineChart>
       <c:dateAx>
-        <c:axId val="479672960"/>
+        <c:axId val="676455936"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -5182,14 +5218,14 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="479678848"/>
+        <c:crossAx val="676457472"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblOffset val="100"/>
         <c:baseTimeUnit val="days"/>
       </c:dateAx>
       <c:valAx>
-        <c:axId val="479678848"/>
+        <c:axId val="676457472"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -5238,7 +5274,7 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="479672960"/>
+        <c:crossAx val="676455936"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -5346,7 +5382,7 @@
         <xdr:cNvPr id="2" name="图表 1">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns="" xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000002000000}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{00000000-0008-0000-0000-000002000000}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -5389,7 +5425,7 @@
         <xdr:cNvPr id="2" name="图表 1">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns="" xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0100-000002000000}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{00000000-0008-0000-0100-000002000000}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -5702,7 +5738,7 @@
   <sheetPr codeName="Sheet1">
     <tabColor rgb="FF00B050"/>
   </sheetPr>
-  <dimension ref="A1:AF115"/>
+  <dimension ref="A1:AF116"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="12"/>
   <cols>
     <col min="1" max="1" width="10" style="1" customWidth="1"/>
@@ -10421,6 +10457,41 @@
         <v>5934.4066689137917</v>
       </c>
     </row>
+    <row r="116" spans="1:11" ht="12.75">
+      <c r="A116" s="15">
+        <v>46234</v>
+      </c>
+      <c r="B116" s="25">
+        <v>1.63802</v>
+      </c>
+      <c r="C116" s="20">
+        <v>1.1794961447368402</v>
+      </c>
+      <c r="D116" s="21">
+        <v>0</v>
+      </c>
+      <c r="E116" s="22">
+        <v>0</v>
+      </c>
+      <c r="F116" s="22">
+        <v>0</v>
+      </c>
+      <c r="G116" s="22">
+        <v>0</v>
+      </c>
+      <c r="H116" s="22">
+        <v>4228.3228496289457</v>
+      </c>
+      <c r="I116" s="22">
+        <v>5934.4066689137917</v>
+      </c>
+      <c r="J116" s="22">
+        <v>1706.083819284846</v>
+      </c>
+      <c r="K116" s="21">
+        <v>5934.4066689137917</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
   <conditionalFormatting sqref="G3">
@@ -10437,7 +10508,7 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A1:AF103"/>
+  <dimension ref="A1:AF104"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="12"/>
   <cols>
     <col min="1" max="1" width="10" style="1" customWidth="1"/>
@@ -14614,6 +14685,41 @@
         <v>9655.027430831773</v>
       </c>
     </row>
+    <row r="104" spans="1:11" ht="12.75">
+      <c r="A104" s="15">
+        <v>46234</v>
+      </c>
+      <c r="B104" s="25">
+        <v>1.63802</v>
+      </c>
+      <c r="C104" s="20">
+        <v>1.8696278799999997</v>
+      </c>
+      <c r="D104" s="21">
+        <v>358.99221399999948</v>
+      </c>
+      <c r="E104" s="22">
+        <v>219.16228983773058</v>
+      </c>
+      <c r="F104" s="22">
+        <v>360.65778074419825</v>
+      </c>
+      <c r="G104" s="22">
+        <v>590.76465801461165</v>
+      </c>
+      <c r="H104" s="22">
+        <v>7502.8270800000037</v>
+      </c>
+      <c r="I104" s="22">
+        <v>10245.792088846385</v>
+      </c>
+      <c r="J104" s="22">
+        <v>2742.9650088463814</v>
+      </c>
+      <c r="K104" s="21">
+        <v>9655.027430831773</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
   <conditionalFormatting sqref="G3">

--- a/lai/valuationquan/AIindex/AIinduindexmodel2.xlsx
+++ b/lai/valuationquan/AIindex/AIinduindexmodel2.xlsx
@@ -758,7 +758,7 @@
               <c:f>'model2(1)mean'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="113"/>
+                <c:ptCount val="114"/>
                 <c:pt idx="0">
                   <c:v>42825</c:v>
                 </c:pt>
@@ -1097,6 +1097,9 @@
                 </c:pt>
                 <c:pt idx="112">
                   <c:v>46234</c:v>
+                </c:pt>
+                <c:pt idx="113">
+                  <c:v>46265</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1106,7 +1109,7 @@
               <c:f>'model2(1)mean'!资金</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="113"/>
+                <c:ptCount val="114"/>
                 <c:pt idx="0">
                   <c:v>27.550142857142728</c:v>
                 </c:pt>
@@ -1444,6 +1447,9 @@
                   <c:v>4228.3228496289457</c:v>
                 </c:pt>
                 <c:pt idx="112">
+                  <c:v>4228.3228496289457</c:v>
+                </c:pt>
+                <c:pt idx="113">
                   <c:v>4228.3228496289457</c:v>
                 </c:pt>
               </c:numCache>
@@ -1487,7 +1493,7 @@
               <c:f>'model2(1)mean'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="113"/>
+                <c:ptCount val="114"/>
                 <c:pt idx="0">
                   <c:v>42825</c:v>
                 </c:pt>
@@ -1826,6 +1832,9 @@
                 </c:pt>
                 <c:pt idx="112">
                   <c:v>46234</c:v>
+                </c:pt>
+                <c:pt idx="113">
+                  <c:v>46265</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1835,7 +1844,7 @@
               <c:f>'model2(1)mean'!资产</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="113"/>
+                <c:ptCount val="114"/>
                 <c:pt idx="1">
                   <c:v>27.550142857142728</c:v>
                 </c:pt>
@@ -2170,6 +2179,9 @@
                   <c:v>5934.4066689137917</c:v>
                 </c:pt>
                 <c:pt idx="112">
+                  <c:v>5934.4066689137917</c:v>
+                </c:pt>
+                <c:pt idx="113">
                   <c:v>5934.4066689137917</c:v>
                 </c:pt>
               </c:numCache>
@@ -2213,7 +2225,7 @@
               <c:f>'model2(1)mean'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="113"/>
+                <c:ptCount val="114"/>
                 <c:pt idx="0">
                   <c:v>42825</c:v>
                 </c:pt>
@@ -2552,6 +2564,9 @@
                 </c:pt>
                 <c:pt idx="112">
                   <c:v>46234</c:v>
+                </c:pt>
+                <c:pt idx="113">
+                  <c:v>46265</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -2561,7 +2576,7 @@
               <c:f>'model2(1)mean'!金额</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="113"/>
+                <c:ptCount val="114"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -2899,6 +2914,9 @@
                   <c:v>1706.083819284846</c:v>
                 </c:pt>
                 <c:pt idx="112">
+                  <c:v>1706.083819284846</c:v>
+                </c:pt>
+                <c:pt idx="113">
                   <c:v>1706.083819284846</c:v>
                 </c:pt>
               </c:numCache>
@@ -2921,11 +2939,11 @@
         </c:dLbls>
         <c:marker val="1"/>
         <c:smooth val="0"/>
-        <c:axId val="508912000"/>
-        <c:axId val="508914304"/>
+        <c:axId val="96969472"/>
+        <c:axId val="96971008"/>
       </c:lineChart>
       <c:dateAx>
-        <c:axId val="508912000"/>
+        <c:axId val="96969472"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -2968,14 +2986,14 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="508914304"/>
+        <c:crossAx val="96971008"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblOffset val="100"/>
         <c:baseTimeUnit val="days"/>
       </c:dateAx>
       <c:valAx>
-        <c:axId val="508914304"/>
+        <c:axId val="96971008"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -3024,7 +3042,7 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="508912000"/>
+        <c:crossAx val="96969472"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -3221,7 +3239,7 @@
               <c:f>'model2(1)MA250'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="101"/>
+                <c:ptCount val="102"/>
                 <c:pt idx="0">
                   <c:v>43189</c:v>
                 </c:pt>
@@ -3524,6 +3542,9 @@
                 </c:pt>
                 <c:pt idx="100">
                   <c:v>46234</c:v>
+                </c:pt>
+                <c:pt idx="101">
+                  <c:v>46265</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -3533,7 +3554,7 @@
               <c:f>'model2(1)MA250'!资金</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="101"/>
+                <c:ptCount val="102"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -3836,6 +3857,9 @@
                 </c:pt>
                 <c:pt idx="100">
                   <c:v>7502.8270800000037</c:v>
+                </c:pt>
+                <c:pt idx="101">
+                  <c:v>7669.4991380000019</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -3878,7 +3902,7 @@
               <c:f>'model2(1)MA250'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="101"/>
+                <c:ptCount val="102"/>
                 <c:pt idx="0">
                   <c:v>43189</c:v>
                 </c:pt>
@@ -4181,6 +4205,9 @@
                 </c:pt>
                 <c:pt idx="100">
                   <c:v>46234</c:v>
+                </c:pt>
+                <c:pt idx="101">
+                  <c:v>46265</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -4190,7 +4217,7 @@
               <c:f>'model2(1)MA250'!资产</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="101"/>
+                <c:ptCount val="102"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -4493,6 +4520,9 @@
                 </c:pt>
                 <c:pt idx="100">
                   <c:v>10245.792088846385</c:v>
+                </c:pt>
+                <c:pt idx="101">
+                  <c:v>10455.815212091835</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -4535,7 +4565,7 @@
               <c:f>'model2(1)MA250'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="101"/>
+                <c:ptCount val="102"/>
                 <c:pt idx="0">
                   <c:v>43189</c:v>
                 </c:pt>
@@ -4838,6 +4868,9 @@
                 </c:pt>
                 <c:pt idx="100">
                   <c:v>46234</c:v>
+                </c:pt>
+                <c:pt idx="101">
+                  <c:v>46265</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -4847,7 +4880,7 @@
               <c:f>'model2(1)MA250'!金额</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="101"/>
+                <c:ptCount val="102"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -5150,6 +5183,9 @@
                 </c:pt>
                 <c:pt idx="100">
                   <c:v>2742.9650088463814</c:v>
+                </c:pt>
+                <c:pt idx="101">
+                  <c:v>2786.3160740918329</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -5171,11 +5207,11 @@
         </c:dLbls>
         <c:marker val="1"/>
         <c:smooth val="0"/>
-        <c:axId val="676455936"/>
-        <c:axId val="676457472"/>
+        <c:axId val="428226816"/>
+        <c:axId val="485507072"/>
       </c:lineChart>
       <c:dateAx>
-        <c:axId val="676455936"/>
+        <c:axId val="428226816"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -5218,14 +5254,14 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="676457472"/>
+        <c:crossAx val="485507072"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblOffset val="100"/>
         <c:baseTimeUnit val="days"/>
       </c:dateAx>
       <c:valAx>
-        <c:axId val="676457472"/>
+        <c:axId val="485507072"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -5274,7 +5310,7 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="676455936"/>
+        <c:crossAx val="428226816"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -5382,7 +5418,7 @@
         <xdr:cNvPr id="2" name="图表 1">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{00000000-0008-0000-0000-000002000000}"/>
+              <a16:creationId xmlns="" xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000002000000}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -5425,7 +5461,7 @@
         <xdr:cNvPr id="2" name="图表 1">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{00000000-0008-0000-0100-000002000000}"/>
+              <a16:creationId xmlns="" xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0100-000002000000}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -5738,7 +5774,7 @@
   <sheetPr codeName="Sheet1">
     <tabColor rgb="FF00B050"/>
   </sheetPr>
-  <dimension ref="A1:AF116"/>
+  <dimension ref="A1:AF117"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="12"/>
   <cols>
     <col min="1" max="1" width="10" style="1" customWidth="1"/>
@@ -10492,6 +10528,41 @@
         <v>5934.4066689137917</v>
       </c>
     </row>
+    <row r="117" spans="1:11" ht="12.75">
+      <c r="A117" s="15">
+        <v>46265</v>
+      </c>
+      <c r="B117" s="25">
+        <v>1.7582200000000001</v>
+      </c>
+      <c r="C117" s="20">
+        <v>1.1845099478487591</v>
+      </c>
+      <c r="D117" s="21">
+        <v>0</v>
+      </c>
+      <c r="E117" s="22">
+        <v>0</v>
+      </c>
+      <c r="F117" s="22">
+        <v>0</v>
+      </c>
+      <c r="G117" s="22">
+        <v>0</v>
+      </c>
+      <c r="H117" s="22">
+        <v>4228.3228496289457</v>
+      </c>
+      <c r="I117" s="22">
+        <v>5934.4066689137917</v>
+      </c>
+      <c r="J117" s="22">
+        <v>1706.083819284846</v>
+      </c>
+      <c r="K117" s="21">
+        <v>5934.4066689137917</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
   <conditionalFormatting sqref="G3">
@@ -10508,7 +10579,7 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A1:AF104"/>
+  <dimension ref="A1:AF105"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="12"/>
   <cols>
     <col min="1" max="1" width="10" style="1" customWidth="1"/>
@@ -14720,6 +14791,41 @@
         <v>9655.027430831773</v>
       </c>
     </row>
+    <row r="105" spans="1:11" ht="12.75">
+      <c r="A105" s="15">
+        <v>46265</v>
+      </c>
+      <c r="B105" s="25">
+        <v>1.7582200000000001</v>
+      </c>
+      <c r="C105" s="20">
+        <v>1.8657503599999992</v>
+      </c>
+      <c r="D105" s="21">
+        <v>166.67205799999851</v>
+      </c>
+      <c r="E105" s="22">
+        <v>94.795906086836979</v>
+      </c>
+      <c r="F105" s="22">
+        <v>455.45368683103521</v>
+      </c>
+      <c r="G105" s="22">
+        <v>800.78778126006273</v>
+      </c>
+      <c r="H105" s="22">
+        <v>7669.4991380000019</v>
+      </c>
+      <c r="I105" s="22">
+        <v>10455.815212091835</v>
+      </c>
+      <c r="J105" s="22">
+        <v>2786.3160740918329</v>
+      </c>
+      <c r="K105" s="21">
+        <v>9655.027430831773</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
   <conditionalFormatting sqref="G3">
